--- a/database/event/3016/event_3016_evp_summary.xlsx
+++ b/database/event/3016/event_3016_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8176</v>
+        <v>6.3619</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3367</v>
+        <v>3.6489</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9288</v>
+        <v>2.0907</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8176</v>
+        <v>6.3619</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0577</v>
+        <v>1.602</v>
       </c>
       <c r="G2" t="n">
         <v>4.7599</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0577</v>
+        <v>1.602</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0577</v>
+        <v>1.602</v>
       </c>
       <c r="J2" t="n">
         <v>4.7599</v>
@@ -529,7 +529,7 @@
         <v>154</v>
       </c>
       <c r="M2" t="n">
-        <v>5.817600000000001</v>
+        <v>6.3619</v>
       </c>
       <c r="N2" t="n">
         <v>201</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4138</v>
+        <v>5.4701</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1051</v>
+        <v>3.1374</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7657</v>
+        <v>1.7354</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4138</v>
+        <v>5.4701</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1198</v>
+        <v>1.1761</v>
       </c>
       <c r="G3" t="n">
         <v>4.294</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1198</v>
+        <v>1.1761</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1198</v>
+        <v>1.1761</v>
       </c>
       <c r="J3" t="n">
         <v>4.294</v>
@@ -575,7 +575,7 @@
         <v>180</v>
       </c>
       <c r="M3" t="n">
-        <v>5.413799999999999</v>
+        <v>5.4701</v>
       </c>
       <c r="N3" t="n">
         <v>225</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7334</v>
+        <v>5.1457</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7149</v>
+        <v>2.9513</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4908</v>
+        <v>1.6061</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7334</v>
+        <v>5.1457</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5351</v>
+        <v>1.9474</v>
       </c>
       <c r="G4" t="n">
         <v>3.1983</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5351</v>
+        <v>1.9474</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5351</v>
+        <v>1.9474</v>
       </c>
       <c r="J4" t="n">
         <v>3.1983</v>
@@ -621,7 +621,7 @@
         <v>154</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7334</v>
+        <v>5.1457</v>
       </c>
       <c r="N4" t="n">
         <v>201</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3223</v>
+        <v>4.6645</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4791</v>
+        <v>2.6753</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3248</v>
+        <v>1.4144</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3223</v>
+        <v>4.6645</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4803</v>
+        <v>1.8225</v>
       </c>
       <c r="G5" t="n">
         <v>2.842</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4803</v>
+        <v>1.8225</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4803</v>
+        <v>1.8225</v>
       </c>
       <c r="J5" t="n">
         <v>2.842</v>
@@ -667,7 +667,7 @@
         <v>154</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3223</v>
+        <v>4.6645</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8095</v>
+        <v>4.336</v>
       </c>
       <c r="C6" t="n">
-        <v>2.185</v>
+        <v>2.4869</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1176</v>
+        <v>1.2836</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8095</v>
+        <v>4.336</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4884</v>
+        <v>1.0149</v>
       </c>
       <c r="G6" t="n">
         <v>3.3211</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4884</v>
+        <v>1.0149</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4884</v>
+        <v>1.0149</v>
       </c>
       <c r="J6" t="n">
         <v>3.3211</v>
@@ -713,7 +713,7 @@
         <v>154</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8095</v>
+        <v>4.336</v>
       </c>
       <c r="N6" t="n">
         <v>201</v>
@@ -722,725 +722,725 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2728</v>
+        <v>3.7156</v>
       </c>
       <c r="C7" t="n">
-        <v>1.8771</v>
+        <v>2.1311</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9008</v>
+        <v>1.0364</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2728</v>
+        <v>3.7156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9829</v>
+        <v>2.4845</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2899</v>
+        <v>1.2311</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9829</v>
+        <v>2.4845</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9829</v>
+        <v>2.4845</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2899</v>
+        <v>1.2311</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2728</v>
+        <v>3.7156</v>
       </c>
       <c r="N7" t="n">
-        <v>225</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1557</v>
+        <v>3.5846</v>
       </c>
       <c r="C8" t="n">
-        <v>1.81</v>
+        <v>2.056</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8535</v>
+        <v>0.9842</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1557</v>
+        <v>3.5846</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8567</v>
+        <v>3.2574</v>
       </c>
       <c r="G8" t="n">
-        <v>2.299</v>
+        <v>0.3272</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8567</v>
+        <v>3.2574</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8567</v>
+        <v>3.2848</v>
       </c>
       <c r="J8" t="n">
-        <v>2.299</v>
+        <v>0.3272</v>
       </c>
       <c r="K8" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="L8" t="n">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1557</v>
+        <v>3.612</v>
       </c>
       <c r="N8" t="n">
-        <v>225</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.057</v>
+        <v>3.5115</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7534</v>
+        <v>2.014</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8136</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.057</v>
+        <v>3.5115</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1059</v>
+        <v>2.496</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0489</v>
+        <v>1.0155</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1059</v>
+        <v>2.496</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1349</v>
+        <v>2.496</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0489</v>
+        <v>1.0155</v>
       </c>
       <c r="K9" t="n">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>3.086</v>
+        <v>3.5115</v>
       </c>
       <c r="N9" t="n">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8945</v>
+        <v>3.3996</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6602</v>
+        <v>1.9499</v>
       </c>
       <c r="D10" t="n">
-        <v>0.748</v>
+        <v>0.9105</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8945</v>
+        <v>3.3996</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6423</v>
+        <v>1.1097</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2522</v>
+        <v>2.2899</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6423</v>
+        <v>1.1097</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6423</v>
+        <v>1.1097</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2522</v>
+        <v>2.2899</v>
       </c>
       <c r="K10" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8945</v>
+        <v>3.3996</v>
       </c>
       <c r="N10" t="n">
-        <v>172</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8359</v>
+        <v>3.1557</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6265</v>
+        <v>1.81</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.8133</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8359</v>
+        <v>3.1557</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6048</v>
+        <v>0.8567</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2311</v>
+        <v>2.299</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6048</v>
+        <v>0.8567</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6048</v>
+        <v>0.8567</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2311</v>
+        <v>2.299</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L11" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8359</v>
+        <v>3.1557</v>
       </c>
       <c r="N11" t="n">
-        <v>170</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6703</v>
+        <v>3.0339</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5316</v>
+        <v>1.7401</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6574</v>
+        <v>0.7648</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6703</v>
+        <v>3.0339</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3431</v>
+        <v>3.0828</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3272</v>
+        <v>-0.0489</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3431</v>
+        <v>3.0828</v>
       </c>
       <c r="I12" t="n">
-        <v>2.354</v>
+        <v>3.1349</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3272</v>
+        <v>-0.0489</v>
       </c>
       <c r="K12" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="L12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6812</v>
+        <v>3.086</v>
       </c>
       <c r="N12" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6675</v>
+        <v>2.8945</v>
       </c>
       <c r="C13" t="n">
-        <v>1.53</v>
+        <v>1.6602</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6562</v>
+        <v>0.7093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6675</v>
+        <v>2.8945</v>
       </c>
       <c r="F13" t="n">
-        <v>1.652</v>
+        <v>0.6423</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0155</v>
+        <v>2.2522</v>
       </c>
       <c r="H13" t="n">
-        <v>1.652</v>
+        <v>0.6423</v>
       </c>
       <c r="I13" t="n">
-        <v>1.652</v>
+        <v>0.6423</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0155</v>
+        <v>2.2522</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L13" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6675</v>
+        <v>2.8945</v>
       </c>
       <c r="N13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6129</v>
+        <v>2.8466</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4986</v>
+        <v>1.6327</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6342</v>
+        <v>0.6902</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6129</v>
+        <v>2.8466</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9357</v>
+        <v>1.3903</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3228</v>
+        <v>1.4563</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9357</v>
+        <v>1.3903</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9631</v>
+        <v>1.3903</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3228</v>
+        <v>1.4563</v>
       </c>
       <c r="K14" t="n">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6403</v>
+        <v>2.8466</v>
       </c>
       <c r="N14" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5959</v>
+        <v>2.5911</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4889</v>
+        <v>1.4861</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6273</v>
+        <v>0.5884</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5959</v>
+        <v>2.5911</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1396</v>
+        <v>2.9139</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4563</v>
+        <v>-0.3228</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1396</v>
+        <v>2.9139</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1396</v>
+        <v>2.9631</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4563</v>
+        <v>-0.3228</v>
       </c>
       <c r="K15" t="n">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5959</v>
+        <v>2.6403</v>
       </c>
       <c r="N15" t="n">
-        <v>170</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3435</v>
+        <v>2.5537</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3441</v>
+        <v>1.4647</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5254</v>
+        <v>0.5735</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3435</v>
+        <v>2.5537</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1756</v>
+        <v>2.1563</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5191</v>
+        <v>0.3974</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1756</v>
+        <v>2.1563</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1756</v>
+        <v>2.1563</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5191</v>
+        <v>0.3974</v>
       </c>
       <c r="K16" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3435</v>
+        <v>2.5537</v>
       </c>
       <c r="N16" t="n">
-        <v>172</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0369</v>
+        <v>2.3898</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1683</v>
+        <v>1.3707</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4015</v>
+        <v>0.5082</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0369</v>
+        <v>2.3898</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7885</v>
+        <v>2.3898</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2484</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7885</v>
+        <v>2.3898</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7968</v>
+        <v>2.3898</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2484</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0452</v>
+        <v>2.3898</v>
       </c>
       <c r="N17" t="n">
-        <v>159</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9327</v>
+        <v>2.3746</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1085</v>
+        <v>1.362</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3594</v>
+        <v>0.5021</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9327</v>
+        <v>2.3746</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5353</v>
+        <v>2.1262</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3974</v>
+        <v>0.2484</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5353</v>
+        <v>2.1262</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5353</v>
+        <v>2.1441</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3974</v>
+        <v>0.2484</v>
       </c>
       <c r="K18" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="L18" t="n">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9327</v>
+        <v>2.3925</v>
       </c>
       <c r="N18" t="n">
-        <v>225</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9082</v>
+        <v>2.3714</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0945</v>
+        <v>1.3601</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3495</v>
+        <v>0.5009</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9082</v>
+        <v>2.3714</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3009</v>
+        <v>2.3769</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6073</v>
+        <v>-0.0055</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3009</v>
+        <v>2.3769</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3009</v>
+        <v>2.3769</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6073</v>
+        <v>-0.0055</v>
       </c>
       <c r="K19" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="L19" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9082</v>
+        <v>2.3714</v>
       </c>
       <c r="N19" t="n">
-        <v>172</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9003</v>
+        <v>2.3435</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0899</v>
+        <v>1.3441</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3463</v>
+        <v>0.4897</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9003</v>
+        <v>2.3435</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1247</v>
+        <v>-0.1756</v>
       </c>
       <c r="G20" t="n">
-        <v>2.025</v>
+        <v>2.5191</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1247</v>
+        <v>-0.1756</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1247</v>
+        <v>-0.1756</v>
       </c>
       <c r="J20" t="n">
-        <v>2.025</v>
+        <v>2.5191</v>
       </c>
       <c r="K20" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="L20" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9003</v>
+        <v>2.3435</v>
       </c>
       <c r="N20" t="n">
-        <v>201</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.8768</v>
+        <v>1.9809</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0764</v>
+        <v>1.1362</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3368</v>
+        <v>0.3453</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8768</v>
+        <v>1.9809</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0193</v>
+        <v>0.9686</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1425</v>
+        <v>1.0123</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0193</v>
+        <v>0.9686</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0382</v>
+        <v>0.9686</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1425</v>
+        <v>1.0123</v>
       </c>
       <c r="K21" t="n">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="L21" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8957</v>
+        <v>1.9809</v>
       </c>
       <c r="N21" t="n">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8668</v>
+        <v>1.9606</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0707</v>
+        <v>1.1245</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3328</v>
+        <v>0.3372</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8668</v>
+        <v>1.9606</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8545</v>
+        <v>1.3533</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0123</v>
+        <v>0.6073</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8545</v>
+        <v>1.3533</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8545</v>
+        <v>1.3533</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0123</v>
+        <v>0.6073</v>
       </c>
       <c r="K22" t="n">
         <v>72</v>
@@ -1449,7 +1449,7 @@
         <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>1.8668</v>
+        <v>1.9606</v>
       </c>
       <c r="N22" t="n">
         <v>172</v>
@@ -1458,541 +1458,541 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8633</v>
+        <v>1.9432</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0687</v>
+        <v>1.1145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3314</v>
+        <v>0.3303</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8633</v>
+        <v>1.9432</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8633</v>
+        <v>1.9432</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8633</v>
+        <v>1.9432</v>
       </c>
       <c r="I23" t="n">
-        <v>1.872</v>
+        <v>1.9432</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.872</v>
+        <v>1.9432</v>
       </c>
       <c r="N23" t="n">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7467</v>
+        <v>1.9003</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0018</v>
+        <v>1.0899</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2843</v>
+        <v>0.3132</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7467</v>
+        <v>1.9003</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7467</v>
+        <v>-0.1247</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.025</v>
       </c>
       <c r="H24" t="n">
-        <v>1.7467</v>
+        <v>-0.1247</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7467</v>
+        <v>-0.1247</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.025</v>
       </c>
       <c r="K24" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7467</v>
+        <v>1.9003</v>
       </c>
       <c r="N24" t="n">
-        <v>122</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.7234</v>
+        <v>1.8618</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9885</v>
+        <v>1.0678</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2749</v>
+        <v>0.2978</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7234</v>
+        <v>1.8618</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7234</v>
+        <v>2.0043</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.1425</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7234</v>
+        <v>2.0043</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7234</v>
+        <v>2.0382</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.1425</v>
       </c>
       <c r="K25" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>1.7234</v>
+        <v>1.8957</v>
       </c>
       <c r="N25" t="n">
-        <v>106</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6034</v>
+        <v>1.8564</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9196</v>
+        <v>1.0647</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2264</v>
+        <v>0.2957</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6034</v>
+        <v>1.8564</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6034</v>
+        <v>1.8564</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6034</v>
+        <v>1.8564</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6109</v>
+        <v>1.872</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6109</v>
+        <v>1.872</v>
       </c>
       <c r="N26" t="n">
-        <v>139</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5912</v>
+        <v>1.7373</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9126</v>
+        <v>0.9964</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2214</v>
+        <v>0.2482</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5912</v>
+        <v>1.7373</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2961</v>
+        <v>2.2169</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2951</v>
+        <v>-0.4796</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2961</v>
+        <v>2.2169</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3082</v>
+        <v>2.2355</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2951</v>
+        <v>-0.4796</v>
       </c>
       <c r="K27" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="L27" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6033</v>
+        <v>1.7559</v>
       </c>
       <c r="N27" t="n">
-        <v>179</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5225</v>
+        <v>1.5975</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8732</v>
+        <v>0.9163</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1937</v>
+        <v>0.1925</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5225</v>
+        <v>1.5975</v>
       </c>
       <c r="F28" t="n">
-        <v>1.528</v>
+        <v>1.5975</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0055</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.528</v>
+        <v>1.5975</v>
       </c>
       <c r="I28" t="n">
-        <v>1.528</v>
+        <v>1.6109</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0055</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="L28" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5225</v>
+        <v>1.6109</v>
       </c>
       <c r="N28" t="n">
-        <v>225</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4952</v>
+        <v>1.5816</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8576</v>
+        <v>0.9071</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1827</v>
+        <v>0.1862</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4952</v>
+        <v>1.5816</v>
       </c>
       <c r="F29" t="n">
-        <v>1.9751</v>
+        <v>1.2865</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4799</v>
+        <v>0.2951</v>
       </c>
       <c r="H29" t="n">
-        <v>1.9751</v>
+        <v>1.2865</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9935</v>
+        <v>1.3082</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4799</v>
+        <v>0.2951</v>
       </c>
       <c r="K29" t="n">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="L29" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5136</v>
+        <v>1.6033</v>
       </c>
       <c r="N29" t="n">
-        <v>214</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.441</v>
+        <v>1.4805</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8265</v>
+        <v>0.8491</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1608</v>
+        <v>0.1459</v>
       </c>
       <c r="E30" t="n">
-        <v>1.441</v>
+        <v>1.4805</v>
       </c>
       <c r="F30" t="n">
-        <v>1.441</v>
+        <v>1.9604</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4799</v>
       </c>
       <c r="H30" t="n">
-        <v>1.441</v>
+        <v>1.9604</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4477</v>
+        <v>1.9935</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4799</v>
       </c>
       <c r="K30" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4477</v>
+        <v>1.5136</v>
       </c>
       <c r="N30" t="n">
-        <v>139</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4184</v>
+        <v>1.4356</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8135</v>
+        <v>0.8234</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1516</v>
+        <v>0.128</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4184</v>
+        <v>1.4356</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1145</v>
+        <v>1.4356</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3039</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1145</v>
+        <v>1.4356</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1249</v>
+        <v>1.4477</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3039</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="L31" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4288</v>
+        <v>1.4477</v>
       </c>
       <c r="N31" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3449</v>
+        <v>1.4101</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7714</v>
+        <v>0.8088</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1219</v>
+        <v>0.1179</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3449</v>
+        <v>1.4101</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8245</v>
+        <v>1.1062</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4796</v>
+        <v>0.3039</v>
       </c>
       <c r="H32" t="n">
-        <v>1.8245</v>
+        <v>1.1062</v>
       </c>
       <c r="I32" t="n">
-        <v>1.833</v>
+        <v>1.1249</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4796</v>
+        <v>0.3039</v>
       </c>
       <c r="K32" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="L32" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3534</v>
+        <v>1.4288</v>
       </c>
       <c r="N32" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2257</v>
+        <v>1.2873</v>
       </c>
       <c r="C33" t="n">
-        <v>0.703</v>
+        <v>0.7383</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0738</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2257</v>
+        <v>1.2873</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2257</v>
+        <v>1.2873</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2257</v>
+        <v>1.2873</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2257</v>
+        <v>1.2873</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2257</v>
+        <v>1.2873</v>
       </c>
       <c r="N33" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2149</v>
+        <v>1.2777</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6968</v>
+        <v>0.7328</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0694</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2149</v>
+        <v>1.2777</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8342000000000001</v>
+        <v>2.2605</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3807</v>
+        <v>-0.9828</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8342000000000001</v>
+        <v>2.2605</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8381</v>
+        <v>2.2795</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3807</v>
+        <v>-0.9828</v>
       </c>
       <c r="K34" t="n">
         <v>108</v>
@@ -2001,7 +2001,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2188</v>
+        <v>1.2967</v>
       </c>
       <c r="N34" t="n">
         <v>154</v>
@@ -2010,461 +2010,461 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1472</v>
+        <v>1.2257</v>
       </c>
       <c r="C35" t="n">
-        <v>0.658</v>
+        <v>0.703</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0421</v>
+        <v>0.0444</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1472</v>
+        <v>1.2257</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1472</v>
+        <v>1.2257</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1472</v>
+        <v>1.2257</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1526</v>
+        <v>1.2257</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1526</v>
+        <v>1.2257</v>
       </c>
       <c r="N35" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1212</v>
+        <v>1.2118</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6431</v>
+        <v>0.695</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0316</v>
+        <v>0.0389</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1212</v>
+        <v>1.2118</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1212</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.3807</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1212</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1212</v>
+        <v>0.8381</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.3807</v>
       </c>
       <c r="K36" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1212</v>
+        <v>1.2188</v>
       </c>
       <c r="N36" t="n">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8226</v>
+        <v>1.1814</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4718</v>
+        <v>0.6776</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0891</v>
+        <v>0.0268</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8226</v>
+        <v>1.1814</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8226</v>
+        <v>1.5599</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.3785</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8226</v>
+        <v>1.5599</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8226</v>
+        <v>1.5599</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.3785</v>
       </c>
       <c r="K37" t="n">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8226</v>
+        <v>1.1814</v>
       </c>
       <c r="N37" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7716</v>
+        <v>1.1429</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4426</v>
+        <v>0.6555</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1097</v>
+        <v>0.0114</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7716</v>
+        <v>1.1429</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7716</v>
+        <v>1.1429</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7716</v>
+        <v>1.1429</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7716</v>
+        <v>1.1526</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7716</v>
+        <v>1.1526</v>
       </c>
       <c r="N38" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7647</v>
+        <v>1.1155</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4386</v>
+        <v>0.6398</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1124</v>
+        <v>0.0005</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7647</v>
+        <v>1.1155</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7647</v>
+        <v>1.416</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.3005</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7647</v>
+        <v>1.416</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7647</v>
+        <v>1.416</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.3005</v>
       </c>
       <c r="K39" t="n">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7647</v>
+        <v>1.1155</v>
       </c>
       <c r="N39" t="n">
-        <v>103</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7639</v>
+        <v>0.8465</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4381</v>
+        <v>0.4855</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1128</v>
+        <v>-0.1067</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7639</v>
+        <v>0.8465</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7467</v>
+        <v>0.8465</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9828</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.7467</v>
+        <v>0.8465</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7548</v>
+        <v>0.8465</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9828</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="L40" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7719999999999999</v>
+        <v>0.8465</v>
       </c>
       <c r="N40" t="n">
-        <v>154</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7328</v>
+        <v>0.8226</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4203</v>
+        <v>0.4718</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1253</v>
+        <v>-0.1162</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7328</v>
+        <v>0.8226</v>
       </c>
       <c r="F41" t="n">
-        <v>1.7328</v>
+        <v>0.8226</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.7328</v>
+        <v>0.8226</v>
       </c>
       <c r="I41" t="n">
-        <v>1.7489</v>
+        <v>0.8226</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L41" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7488999999999999</v>
+        <v>0.8226</v>
       </c>
       <c r="N41" t="n">
-        <v>179</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7274</v>
+        <v>0.7647</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4172</v>
+        <v>0.4386</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1275</v>
+        <v>-0.1393</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7274</v>
+        <v>0.7647</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7274</v>
+        <v>0.7647</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7274</v>
+        <v>0.7647</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7308</v>
+        <v>0.7647</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7308</v>
+        <v>0.7647</v>
       </c>
       <c r="N42" t="n">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7235</v>
+        <v>0.7247</v>
       </c>
       <c r="C43" t="n">
-        <v>0.415</v>
+        <v>0.4157</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1291</v>
+        <v>-0.1552</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7235</v>
+        <v>0.7247</v>
       </c>
       <c r="F43" t="n">
-        <v>1.102</v>
+        <v>0.7247</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.3785</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.102</v>
+        <v>0.7247</v>
       </c>
       <c r="I43" t="n">
-        <v>1.102</v>
+        <v>0.7308</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.3785</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="L43" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7235</v>
+        <v>0.7308</v>
       </c>
       <c r="N43" t="n">
-        <v>170</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7129</v>
+        <v>0.7199</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4089</v>
+        <v>0.4129</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1334</v>
+        <v>-0.1571</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7129</v>
+        <v>0.7199</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0134</v>
+        <v>1.7199</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.3005</v>
+        <v>-1</v>
       </c>
       <c r="H44" t="n">
-        <v>1.0134</v>
+        <v>1.7199</v>
       </c>
       <c r="I44" t="n">
-        <v>1.0134</v>
+        <v>1.7489</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3005</v>
+        <v>-1</v>
       </c>
       <c r="K44" t="n">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="L44" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7129000000000001</v>
+        <v>0.7488999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45">
@@ -2480,7 +2480,7 @@
         <v>0.3834</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1513</v>
+        <v>-0.1776</v>
       </c>
       <c r="E45" t="n">
         <v>0.6685</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5496</v>
+        <v>0.5476</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3152</v>
+        <v>0.3141</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1993</v>
+        <v>-0.2257</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5496</v>
+        <v>0.5476</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5496</v>
+        <v>0.5476</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5496</v>
+        <v>0.5476</v>
       </c>
       <c r="I46" t="n">
         <v>0.5522</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4964</v>
+        <v>0.4864</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2847</v>
+        <v>0.279</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2208</v>
+        <v>-0.2501</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4964</v>
+        <v>0.4864</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3385</v>
+        <v>1.3285</v>
       </c>
       <c r="G47" t="n">
         <v>-0.8421</v>
       </c>
       <c r="H47" t="n">
-        <v>1.3385</v>
+        <v>1.3285</v>
       </c>
       <c r="I47" t="n">
         <v>1.351</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4681</v>
+        <v>0.4626</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2685</v>
+        <v>0.2653</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2323</v>
+        <v>-0.2596</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4681</v>
+        <v>0.4626</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4681</v>
+        <v>1.4626</v>
       </c>
       <c r="G48" t="n">
         <v>-1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.4681</v>
+        <v>1.4626</v>
       </c>
       <c r="I48" t="n">
         <v>1.4749</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3666</v>
+        <v>0.3652</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2103</v>
+        <v>0.2095</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2733</v>
+        <v>-0.2984</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3666</v>
+        <v>0.3652</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3666</v>
+        <v>0.3652</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3666</v>
+        <v>0.3652</v>
       </c>
       <c r="I49" t="n">
         <v>0.3683</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.262</v>
+        <v>0.2599</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1503</v>
+        <v>0.1491</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3155</v>
+        <v>-0.3404</v>
       </c>
       <c r="E50" t="n">
-        <v>0.262</v>
+        <v>0.2599</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5744</v>
+        <v>0.5723</v>
       </c>
       <c r="G50" t="n">
         <v>-0.3124</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5744</v>
+        <v>0.5723</v>
       </c>
       <c r="I50" t="n">
         <v>0.5770999999999999</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1406</v>
+        <v>0.1519</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0806</v>
+        <v>0.0871</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3646</v>
+        <v>-0.3834</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1406</v>
+        <v>0.1519</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1406</v>
+        <v>0.1519</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1406</v>
+        <v>0.1519</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1406</v>
+        <v>0.1519</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1406</v>
+        <v>0.1519</v>
       </c>
       <c r="N51" t="n">
         <v>122</v>
@@ -2802,7 +2802,7 @@
         <v>0.0716</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3709</v>
+        <v>-0.3942</v>
       </c>
       <c r="E52" t="n">
         <v>0.1249</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0258</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4395</v>
+        <v>-0.4618</v>
       </c>
       <c r="E53" t="n">
         <v>-0.045</v>
@@ -2894,7 +2894,7 @@
         <v>-0.06419999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4666</v>
+        <v>-0.4885</v>
       </c>
       <c r="E54" t="n">
         <v>-0.1119</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3033</v>
+        <v>-0.3022</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.174</v>
+        <v>-0.1733</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.5643</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3033</v>
+        <v>-0.3022</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3033</v>
+        <v>-0.3022</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3033</v>
+        <v>-0.3022</v>
       </c>
       <c r="I55" t="n">
         <v>-0.3047</v>
@@ -2986,7 +2986,7 @@
         <v>-0.189</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5545</v>
+        <v>-0.5752</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3296</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2445</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5936</v>
+        <v>-0.6137</v>
       </c>
       <c r="E57" t="n">
         <v>-0.4263</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3007</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6331</v>
+        <v>-0.6528</v>
       </c>
       <c r="E58" t="n">
         <v>-0.5242</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5758</v>
+        <v>-0.5762</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3303</v>
+        <v>-0.3305</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.654</v>
+        <v>-0.6735</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5758</v>
+        <v>-0.5762</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1103</v>
+        <v>0.1099</v>
       </c>
       <c r="G59" t="n">
         <v>-0.6861</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1103</v>
+        <v>0.1099</v>
       </c>
       <c r="I59" t="n">
         <v>0.1108</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3402</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.661</v>
+        <v>-0.6802</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5931999999999999</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6206</v>
+        <v>-0.5995</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3559</v>
+        <v>-0.3438</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6721</v>
+        <v>-0.6828</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6206</v>
+        <v>-0.5995</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0588</v>
+        <v>-0.0377</v>
       </c>
       <c r="G61" t="n">
         <v>-0.5618</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0588</v>
+        <v>-0.0377</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0593</v>
+        <v>-0.0383</v>
       </c>
       <c r="J61" t="n">
         <v>-0.5618</v>
@@ -3243,7 +3243,7 @@
         <v>49</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.6211</v>
+        <v>-0.6001</v>
       </c>
       <c r="N61" t="n">
         <v>214</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3713</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6829</v>
+        <v>-0.7018</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6473</v>
@@ -3308,7 +3308,7 @@
         <v>-0.3826</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6909</v>
+        <v>-0.7097</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6671</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4175</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7154</v>
+        <v>-0.7339</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7279</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4568</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7431</v>
+        <v>-0.7612</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7965</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4581</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.744</v>
+        <v>-0.7621</v>
       </c>
       <c r="E66" t="n">
         <v>-0.7987</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4928</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7685</v>
+        <v>-0.7862</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8592</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5247000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7909</v>
+        <v>-0.8084</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9147999999999999</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5255</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7915</v>
+        <v>-0.8089</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9162</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5967</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8417</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0404</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6011</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8448</v>
+        <v>-0.8615</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0481</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1162</v>
+        <v>-1.1154</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6402</v>
+        <v>-0.6397</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8723</v>
+        <v>-0.8883</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1162</v>
+        <v>-1.1154</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1162</v>
+        <v>-0.1154</v>
       </c>
       <c r="G72" t="n">
         <v>-1</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.1162</v>
+        <v>-0.1154</v>
       </c>
       <c r="I72" t="n">
         <v>-0.1173</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6696</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.893</v>
+        <v>-0.909</v>
       </c>
       <c r="E73" t="n">
         <v>-1.1674</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7305</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9359</v>
+        <v>-0.9513</v>
       </c>
       <c r="E74" t="n">
         <v>-1.2736</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.3116</v>
+        <v>-1.3067</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7523</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9512</v>
+        <v>-0.9645</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.3116</v>
+        <v>-1.3067</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3116</v>
+        <v>-1.3067</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3116</v>
+        <v>-1.3067</v>
       </c>
       <c r="I75" t="n">
         <v>-1.3177</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7909</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9784</v>
+        <v>-0.9933</v>
       </c>
       <c r="E76" t="n">
         <v>-1.379</v>
@@ -3952,7 +3952,7 @@
         <v>-0.8085</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9908</v>
+        <v>-1.0055</v>
       </c>
       <c r="E77" t="n">
         <v>-1.4096</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8491</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0194</v>
+        <v>-1.0337</v>
       </c>
       <c r="E78" t="n">
         <v>-1.4804</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8576</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0254</v>
+        <v>-1.0396</v>
       </c>
       <c r="E79" t="n">
         <v>-1.4953</v>
@@ -4090,7 +4090,7 @@
         <v>-0.8583</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0259</v>
+        <v>-1.0401</v>
       </c>
       <c r="E80" t="n">
         <v>-1.4964</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.6005</v>
+        <v>-2.5908</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.4915</v>
+        <v>-1.486</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4719</v>
+        <v>-1.4761</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.6005</v>
+        <v>-2.5908</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.6005</v>
+        <v>-2.5908</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.6005</v>
+        <v>-2.5908</v>
       </c>
       <c r="I81" t="n">
         <v>-2.6126</v>
